--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:29:54+00:00</t>
+          <t>2026-05-10T00:27:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:27:13+00:00</t>
+          <t>2026-05-11T00:27:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:41+00:00</t>
+          <t>2026-05-12T00:28:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:28:10+00:00</t>
+          <t>2026-05-13T00:30:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:30:43+00:00</t>
+          <t>2026-05-14T00:31:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:31:42+00:00</t>
+          <t>2026-05-15T00:29:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:29:18+00:00</t>
+          <t>2026-05-16T00:27:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:57+00:00</t>
+          <t>2026-05-17T00:28:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:49+00:00</t>
+          <t>2026-05-18T00:29:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:22+00:00</t>
+          <t>2026-05-19T00:32:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:48+00:00</t>
+          <t>2026-05-20T00:34:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:34:23+00:00</t>
+          <t>2026-05-21T00:35:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21T00:35:11+00:00</t>
+          <t>2026-05-22T00:32:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:32:33+00:00</t>
+          <t>2026-05-23T00:33:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:33:22+00:00</t>
+          <t>2026-05-24T00:31:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:31:58+00:00</t>
+          <t>2026-05-25T00:34:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:34:18+00:00</t>
+          <t>2026-05-26T00:34:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:34:03+00:00</t>
+          <t>2026-05-27T00:33:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:57+00:00</t>
+          <t>2026-05-28T00:30:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:30:28+00:00</t>
+          <t>2026-05-29T00:36:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:36:36+00:00</t>
+          <t>2026-05-30T00:33:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:33:03+00:00</t>
+          <t>2026-05-31T00:34:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:34:19+00:00</t>
+          <t>2026-06-01T00:36:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:36:54+00:00</t>
+          <t>2026-06-02T00:40:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:40:41+00:00</t>
+          <t>2026-06-03T00:45:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:45:42+00:00</t>
+          <t>2026-06-04T00:43:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:40+00:00</t>
+          <t>2026-06-05T00:36:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:53+00:00</t>
+          <t>2026-06-06T00:34:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:52+00:00</t>
+          <t>2026-06-07T00:35:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:53+00:00</t>
+          <t>2026-06-08T00:37:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:37:24+00:00</t>
+          <t>2026-06-09T00:32:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:32:33+00:00</t>
+          <t>2026-06-10T00:38:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:38:28+00:00</t>
+          <t>2026-06-11T00:42:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:42:43+00:00</t>
+          <t>2026-06-12T00:48:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:48:13+00:00</t>
+          <t>2026-06-13T00:39:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:39:29+00:00</t>
+          <t>2026-06-14T00:38:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:38:16+00:00</t>
+          <t>2026-06-15T00:39:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:39:30+00:00</t>
+          <t>2026-06-16T00:50:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:50:06+00:00</t>
+          <t>2026-06-17T00:40:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:40:07+00:00</t>
+          <t>2026-06-18T00:44:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:44:09+00:00</t>
+          <t>2026-06-19T00:44:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:44:09+00:00</t>
+          <t>2026-06-20T00:36:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:36:21+00:00</t>
+          <t>2026-06-21T00:39:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:39:23+00:00</t>
+          <t>2026-06-22T00:38:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:38:25+00:00</t>
+          <t>2026-06-23T00:36:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:36:20+00:00</t>
+          <t>2026-06-24T00:30:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24T00:30:38+00:00</t>
+          <t>2026-06-25T00:35:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:35:39+00:00</t>
+          <t>2026-06-26T00:41:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:41:57+00:00</t>
+          <t>2026-06-27T00:33:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:33:24+00:00</t>
+          <t>2026-06-28T00:33:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:33:21+00:00</t>
+          <t>2026-06-29T00:35:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:35:30+00:00</t>
+          <t>2026-06-30T00:33:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:57+00:00</t>
+          <t>2026-07-01T00:38:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:38:42+00:00</t>
+          <t>2026-07-02T00:33:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:46+00:00</t>
+          <t>2026-07-03T02:05:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:57+00:00</t>
+          <t>2026-07-04T02:03:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:03:28+00:00</t>
+          <t>2026-07-05T02:11:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:11:26+00:00</t>
+          <t>2026-07-06T02:16:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:16:22+00:00</t>
+          <t>2026-07-07T02:11:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:39+00:00</t>
+          <t>2026-07-08T01:53:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:53:16+00:00</t>
+          <t>2026-07-09T02:06:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:06:18+00:00</t>
+          <t>2026-07-10T02:04:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:04:51+00:00</t>
+          <t>2026-07-11T01:51:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:51:28+00:00</t>
+          <t>2026-07-12T01:54:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:54:15+00:00</t>
+          <t>2026-07-13T01:56:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:56:51+00:00</t>
+          <t>2026-07-14T01:43:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:43:55+00:00</t>
+          <t>2026-07-15T01:29:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:29:31+00:00</t>
+          <t>2026-07-16T01:50:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16T01:50:08+00:00</t>
+          <t>2026-07-17T01:53:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:53:38+00:00</t>
+          <t>2026-07-18T01:44:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:44:06+00:00</t>
+          <t>2026-07-19T01:52:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:52:11+00:00</t>
+          <t>2026-07-20T03:26:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:26:05+00:00</t>
+          <t>2026-07-21T01:55:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21T01:55:51+00:00</t>
+          <t>2026-07-22T01:51:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:51:05+00:00</t>
+          <t>2026-07-23T01:59:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:59:46+00:00</t>
+          <t>2026-07-24T01:55:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:55:04+00:00</t>
+          <t>2026-07-25T01:53:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:53:43+00:00</t>
+          <t>2026-07-26T01:57:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:57:28+00:00</t>
+          <t>2026-07-27T02:07:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:07:56+00:00</t>
+          <t>2026-07-28T01:47:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:47:26+00:00</t>
+          <t>2026-07-29T01:49:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:49:16+00:00</t>
+          <t>2026-07-30T01:32:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:32:47+00:00</t>
+          <t>2026-07-31T01:58:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:58:55+00:00</t>
+          <t>2026-08-01T02:01:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T02:01:09+00:00</t>
+          <t>2026-08-02T01:55:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:55:18+00:00</t>
+          <t>2026-08-03T01:58:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:58:01+00:00</t>
+          <t>2026-08-04T01:45:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:45:04+00:00</t>
+          <t>2026-08-05T01:46:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:46:20+00:00</t>
+          <t>2026-08-06T01:46:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:46:49+00:00</t>
+          <t>2026-08-07T02:11:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:11:15+00:00</t>
+          <t>2026-08-08T00:58:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:58:12+00:00</t>
+          <t>2026-08-09T01:02:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:02:28+00:00</t>
+          <t>2026-08-10T01:04:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:04:38+00:00</t>
+          <t>2026-08-11T01:02:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:58+00:00</t>
+          <t>2026-08-12T01:10:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:10:35+00:00</t>
+          <t>2026-08-13T01:12:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:12:50+00:00</t>
+          <t>2026-08-14T01:10:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:46+00:00</t>
+          <t>2026-08-15T00:44:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:44:21+00:00</t>
+          <t>2026-08-16T00:45:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:45:19+00:00</t>
+          <t>2026-08-17T00:43:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:43:36+00:00</t>
+          <t>2026-08-17T06:43:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:43:50+00:00</t>
+          <t>2026-08-17T06:56:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:56:02+00:00</t>
+          <t>2026-08-17T07:43:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:43:32+00:00</t>
+          <t>2026-08-17T08:01:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:01:08+00:00</t>
+          <t>2026-08-17T08:14:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:14:33+00:00</t>
+          <t>2026-08-17T08:29:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:29:50+00:00</t>
+          <t>2026-08-17T09:22:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:22:08+00:00</t>
+          <t>2026-08-17T09:27:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:27:33+00:00</t>
+          <t>2026-08-17T10:46:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:46:14+00:00</t>
+          <t>2026-08-17T12:52:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:52:41+00:00</t>
+          <t>2026-08-17T23:15:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:15:13+00:00</t>
+          <t>2026-08-18T05:53:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:53:43+00:00</t>
+          <t>2026-08-18T23:15:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:15:22+00:00</t>
+          <t>2026-08-19T23:16:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:16:04+00:00</t>
+          <t>2026-08-20T23:18:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:18:39+00:00</t>
+          <t>2026-08-21T23:16:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:16:08+00:00</t>
+          <t>2026-08-22T23:13:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:13:59+00:00</t>
+          <t>2026-08-23T23:13:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:13:33+00:00</t>
+          <t>2026-08-24T23:16:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:16:38+00:00</t>
+          <t>2026-08-25T23:18:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:18:26+00:00</t>
+          <t>2026-08-27T04:10:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:10:35+00:00</t>
+          <t>2026-08-28T06:27:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:27:08+00:00</t>
+          <t>2026-08-29T03:59:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:59:25+00:00</t>
+          <t>2026-08-30T00:57:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:57:00+00:00</t>
+          <t>2026-08-31T01:01:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:01:37+00:00</t>
+          <t>2026-09-01T01:32:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:32:07+00:00</t>
+          <t>2026-09-02T00:42:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:42:03+00:00</t>
+          <t>2026-09-03T00:53:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:53:56+00:00</t>
+          <t>2026-09-04T00:34:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:34:16+00:00</t>
+          <t>2026-09-05T00:31:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:31:40+00:00</t>
+          <t>2026-09-06T00:24:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:33+00:00</t>
+          <t>2026-09-07T00:31:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:31:48+00:00</t>
+          <t>2026-09-07T07:50:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:50:08+00:00</t>
+          <t>2026-09-07T09:43:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:43:39+00:00</t>
+          <t>2026-09-07T11:03:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:03:18+00:00</t>
+          <t>2026-09-08T00:50:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:50:40+00:00</t>
+          <t>2026-09-09T00:54:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:54:29+00:00</t>
+          <t>2026-09-09T01:46:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:46:01+00:00</t>
+          <t>2026-09-09T02:38:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:57+00:00</t>
+          <t>2026-09-10T00:44:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:44:37+00:00</t>
+          <t>2026-09-11T00:42:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:42:56+00:00</t>
+          <t>2026-09-12T00:50:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:50:55+00:00</t>
+          <t>2026-09-13T00:31:30+00:00</t>
         </is>
       </c>
     </row>
